--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_lagos.xlsx
@@ -404,7 +404,7 @@
         <v>26.47399841450459</v>
       </c>
       <c r="D2">
-        <v>1.952234060473343</v>
+        <v>4.040507266903449</v>
       </c>
       <c r="E2">
         <v>16.3661002442808</v>
@@ -429,7 +429,7 @@
         <v>26.34119948391393</v>
       </c>
       <c r="D3">
-        <v>1.628507523383489</v>
+        <v>2.85186943620178</v>
       </c>
       <c r="E3">
         <v>21.72455583919961</v>
@@ -454,7 +454,7 @@
         <v>23.8349885408709</v>
       </c>
       <c r="D4">
-        <v>1.372117400419287</v>
+        <v>2.038940809968847</v>
       </c>
       <c r="E4">
         <v>28.36942112240389</v>
@@ -479,7 +479,7 @@
         <v>26.35361169619626</v>
       </c>
       <c r="D5">
-        <v>1.436120996441281</v>
+        <v>2.31062124248497</v>
       </c>
       <c r="E5">
         <v>25.51311080271712</v>
@@ -504,7 +504,7 @@
         <v>29.84779600711603</v>
       </c>
       <c r="D6">
-        <v>1.588549298723048</v>
+        <v>3.020899681528662</v>
       </c>
       <c r="E6">
         <v>20.31458493388864</v>
@@ -529,7 +529,7 @@
         <v>26.65741062131205</v>
       </c>
       <c r="D7">
-        <v>1.478383579217447</v>
+        <v>2.439974592420072</v>
       </c>
       <c r="E7">
         <v>24.44743516745174</v>
@@ -554,7 +554,7 @@
         <v>25.83876980428705</v>
       </c>
       <c r="D8">
-        <v>1.662062733961533</v>
+        <v>2.913122171945701</v>
       </c>
       <c r="E8">
         <v>21.43238132182515</v>
@@ -579,7 +579,7 @@
         <v>23.81385019180295</v>
       </c>
       <c r="D9">
-        <v>1.449729255085614</v>
+        <v>2.214126061689763</v>
       </c>
       <c r="E9">
         <v>26.72800047792581</v>
@@ -604,7 +604,7 @@
         <v>27.13987473903967</v>
       </c>
       <c r="D10">
-        <v>1.817923051378149</v>
+        <v>3.588350969191872</v>
       </c>
       <c r="E10">
         <v>17.97841714506978</v>
@@ -629,7 +629,7 @@
         <v>23.34688459304737</v>
       </c>
       <c r="D11">
-        <v>1.976765799256506</v>
+        <v>3.670964467005076</v>
       </c>
       <c r="E11">
         <v>18.0896585921287</v>
@@ -654,7 +654,7 @@
         <v>22.94123509284789</v>
       </c>
       <c r="D12">
-        <v>1.691464853627016</v>
+        <v>2.764025342025526</v>
       </c>
       <c r="E12">
         <v>22.73695198329854</v>
@@ -679,7 +679,7 @@
         <v>23.13242410910691</v>
       </c>
       <c r="D13">
-        <v>1.879444352571523</v>
+        <v>3.325043885313049</v>
       </c>
       <c r="E13">
         <v>19.63014013324144</v>
@@ -704,7 +704,7 @@
         <v>23.56541698546289</v>
       </c>
       <c r="D14">
-        <v>1.656527249683143</v>
+        <v>2.717255717255717</v>
       </c>
       <c r="E14">
         <v>22.94847328244275</v>
@@ -729,7 +729,7 @@
         <v>25.77706323687031</v>
       </c>
       <c r="D15">
-        <v>1.833606288896168</v>
+        <v>3.477018633540373</v>
       </c>
       <c r="E15">
         <v>18.61056525257196</v>
@@ -754,7 +754,7 @@
         <v>22.00938232994527</v>
       </c>
       <c r="D16">
-        <v>1.574153846153846</v>
+        <v>2.408662900188324</v>
       </c>
       <c r="E16">
         <v>25.38847716949558</v>
@@ -779,7 +779,7 @@
         <v>24.10901467505241</v>
       </c>
       <c r="D17">
-        <v>1.653379549393414</v>
+        <v>2.749279538904899</v>
       </c>
       <c r="E17">
         <v>22.66492488569563</v>
@@ -804,7 +804,7 @@
         <v>26.58402838578867</v>
       </c>
       <c r="D18">
-        <v>2.055213561890331</v>
+        <v>4.530480167014614</v>
       </c>
       <c r="E18">
         <v>14.84810911345319</v>
@@ -829,7 +829,7 @@
         <v>21.87445357579996</v>
       </c>
       <c r="D19">
-        <v>1.610985915492958</v>
+        <v>2.487603305785124</v>
       </c>
       <c r="E19">
         <v>24.80310713129787</v>
@@ -854,7 +854,7 @@
         <v>21.03383458646617</v>
       </c>
       <c r="D20">
-        <v>1.68141592920354</v>
+        <v>2.601466992665037</v>
       </c>
       <c r="E20">
         <v>24.10419613389911</v>
@@ -879,7 +879,7 @@
         <v>24.64462134404208</v>
       </c>
       <c r="D21">
-        <v>1.739552423343224</v>
+        <v>3.044934397402949</v>
       </c>
       <c r="E21">
         <v>20.85354845988943</v>
@@ -904,7 +904,7 @@
         <v>25.66574089201111</v>
       </c>
       <c r="D22">
-        <v>1.535624686402408</v>
+        <v>2.534575569358178</v>
       </c>
       <c r="E22">
         <v>23.89433066191748</v>
@@ -929,7 +929,7 @@
         <v>26.40038192234246</v>
       </c>
       <c r="D23">
-        <v>1.436671239140375</v>
+        <v>2.314548802946593</v>
       </c>
       <c r="E23">
         <v>25.47382248076562</v>
@@ -954,7 +954,7 @@
         <v>22.52729778437401</v>
       </c>
       <c r="D24">
-        <v>1.645960565346362</v>
+        <v>2.6159179145868</v>
       </c>
       <c r="E24">
         <v>23.78000527565286</v>
@@ -979,7 +979,7 @@
         <v>24.31580018313155</v>
       </c>
       <c r="D25">
-        <v>1.482503770739065</v>
+        <v>2.31816037735849</v>
       </c>
       <c r="E25">
         <v>25.76098183364724</v>
@@ -1004,7 +1004,7 @@
         <v>23.68896925858951</v>
       </c>
       <c r="D26">
-        <v>1.370696777747177</v>
+        <v>2.029771615008157</v>
       </c>
       <c r="E26">
         <v>28.48513011152416</v>
@@ -1029,7 +1029,7 @@
         <v>22.39271457085828</v>
       </c>
       <c r="D27">
-        <v>1.529187333078977</v>
+        <v>2.32550043516101</v>
       </c>
       <c r="E27">
         <v>25.99939659073767</v>
@@ -1054,7 +1054,7 @@
         <v>23.35234474017744</v>
       </c>
       <c r="D28">
-        <v>1.755283648498332</v>
+        <v>2.974552309142318</v>
       </c>
       <c r="E28">
         <v>21.4170367379895</v>
@@ -1079,7 +1079,7 @@
         <v>28.21345707656612</v>
       </c>
       <c r="D29">
-        <v>1.611817501869858</v>
+        <v>2.956104252400549</v>
       </c>
       <c r="E29">
         <v>20.87628865979381</v>
@@ -1104,7 +1104,7 @@
         <v>22.27672955974843</v>
       </c>
       <c r="D30">
-        <v>1.923542221146867</v>
+        <v>3.365791701947502</v>
       </c>
       <c r="E30">
         <v>19.54812546553008</v>
@@ -1129,7 +1129,7 @@
         <v>23.4375</v>
       </c>
       <c r="D31">
-        <v>1.598335067637877</v>
+        <v>2.555740432612313</v>
       </c>
       <c r="E31">
         <v>24.06888265919103</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.47399841450459</v>
+      </c>
+      <c r="C2">
         <v>24.74936768932919</v>
-      </c>
-      <c r="C2">
-        <v>26.47399841450459</v>
       </c>
       <c r="D2">
         <v>4.040507266903449</v>
       </c>
       <c r="E2">
-        <v>16.3661002442808</v>
+        <v>17.50655278783232</v>
       </c>
       <c r="F2">
         <v>66.12734696788688</v>
       </c>
       <c r="G2">
-        <v>17.50655278783232</v>
+        <v>16.3661002442808</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>26.34119948391393</v>
+      </c>
+      <c r="C3">
         <v>35.06471885795147</v>
-      </c>
-      <c r="C3">
-        <v>26.34119948391393</v>
       </c>
       <c r="D3">
         <v>2.85186943620178</v>
       </c>
       <c r="E3">
-        <v>21.72455583919961</v>
+        <v>16.31984734792811</v>
       </c>
       <c r="F3">
         <v>61.95559681287228</v>
       </c>
       <c r="G3">
-        <v>16.31984734792811</v>
+        <v>21.72455583919961</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>23.8349885408709</v>
+      </c>
+      <c r="C4">
         <v>49.04507257448434</v>
-      </c>
-      <c r="C4">
-        <v>23.8349885408709</v>
       </c>
       <c r="D4">
         <v>2.038940809968847</v>
       </c>
       <c r="E4">
+        <v>13.7870083959346</v>
+      </c>
+      <c r="F4">
+        <v>57.84357048166151</v>
+      </c>
+      <c r="G4">
         <v>28.36942112240389</v>
-      </c>
-      <c r="F4">
-        <v>57.84357048166152</v>
-      </c>
-      <c r="G4">
-        <v>13.7870083959346</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.35361169619626</v>
+      </c>
+      <c r="C5">
         <v>43.27840416305291</v>
-      </c>
-      <c r="C5">
-        <v>26.35361169619626</v>
       </c>
       <c r="D5">
         <v>2.31062124248497</v>
       </c>
       <c r="E5">
-        <v>25.51311080271712</v>
+        <v>15.53575341465196</v>
       </c>
       <c r="F5">
         <v>58.95113578263092</v>
       </c>
       <c r="G5">
-        <v>15.53575341465196</v>
+        <v>25.51311080271712</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.84779600711603</v>
+      </c>
+      <c r="C6">
         <v>33.10272122290308</v>
-      </c>
-      <c r="C6">
-        <v>29.84779600711603</v>
       </c>
       <c r="D6">
         <v>3.020899681528662</v>
       </c>
       <c r="E6">
-        <v>20.31458493388864</v>
+        <v>18.3170919089402</v>
       </c>
       <c r="F6">
         <v>61.36832315717116</v>
       </c>
       <c r="G6">
-        <v>18.3170919089402</v>
+        <v>20.31458493388864</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.65741062131205</v>
+      </c>
+      <c r="C7">
         <v>40.98403332176328</v>
-      </c>
-      <c r="C7">
-        <v>26.65741062131205</v>
       </c>
       <c r="D7">
         <v>2.439974592420072</v>
       </c>
       <c r="E7">
-        <v>24.44743516745174</v>
+        <v>15.9014441741291</v>
       </c>
       <c r="F7">
-        <v>59.65112065841918</v>
+        <v>59.65112065841917</v>
       </c>
       <c r="G7">
-        <v>15.9014441741291</v>
+        <v>24.44743516745173</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>25.83876980428705</v>
+      </c>
+      <c r="C8">
         <v>34.32743087915502</v>
-      </c>
-      <c r="C8">
-        <v>25.83876980428705</v>
       </c>
       <c r="D8">
         <v>2.913122171945701</v>
       </c>
       <c r="E8">
-        <v>21.43238132182515</v>
+        <v>16.1324734519711</v>
       </c>
       <c r="F8">
         <v>62.43514522620375</v>
       </c>
       <c r="G8">
-        <v>16.1324734519711</v>
+        <v>21.43238132182515</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.81385019180295</v>
+      </c>
+      <c r="C9">
         <v>45.16454673934989</v>
-      </c>
-      <c r="C9">
-        <v>23.81385019180295</v>
       </c>
       <c r="D9">
         <v>2.214126061689763</v>
       </c>
       <c r="E9">
-        <v>26.72800047792581</v>
+        <v>14.09283708704224</v>
       </c>
       <c r="F9">
         <v>59.17916243503197</v>
       </c>
       <c r="G9">
-        <v>14.09283708704224</v>
+        <v>26.72800047792581</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.13987473903967</v>
+      </c>
+      <c r="C10">
         <v>27.86795407098121</v>
-      </c>
-      <c r="C10">
-        <v>27.13987473903967</v>
       </c>
       <c r="D10">
         <v>3.588350969191872</v>
       </c>
       <c r="E10">
-        <v>17.97841714506978</v>
+        <v>17.5087122678833</v>
       </c>
       <c r="F10">
         <v>64.51287058704692</v>
       </c>
       <c r="G10">
-        <v>17.5087122678833</v>
+        <v>17.97841714506978</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>23.34688459304737</v>
+      </c>
+      <c r="C11">
         <v>27.24079758842888</v>
-      </c>
-      <c r="C11">
-        <v>23.34688459304737</v>
       </c>
       <c r="D11">
         <v>3.670964467005076</v>
       </c>
       <c r="E11">
-        <v>18.0896585921287</v>
+        <v>15.50384749591376</v>
       </c>
       <c r="F11">
         <v>66.40649391195754</v>
       </c>
       <c r="G11">
-        <v>15.50384749591376</v>
+        <v>18.0896585921287</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>22.94123509284789</v>
+      </c>
+      <c r="C12">
         <v>36.17911836029631</v>
-      </c>
-      <c r="C12">
-        <v>22.94123509284789</v>
       </c>
       <c r="D12">
         <v>2.764025342025526</v>
       </c>
       <c r="E12">
-        <v>22.73695198329854</v>
+        <v>14.41753653444676</v>
       </c>
       <c r="F12">
         <v>62.84551148225469</v>
       </c>
       <c r="G12">
-        <v>14.41753653444676</v>
+        <v>22.73695198329854</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>23.13242410910691</v>
+      </c>
+      <c r="C13">
         <v>30.07479102507699</v>
-      </c>
-      <c r="C13">
-        <v>23.13242410910691</v>
       </c>
       <c r="D13">
         <v>3.325043885313049</v>
       </c>
       <c r="E13">
-        <v>19.63014013324144</v>
+        <v>15.09878244888582</v>
       </c>
       <c r="F13">
         <v>65.27107741787273</v>
       </c>
       <c r="G13">
-        <v>15.09878244888582</v>
+        <v>19.63014013324144</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>23.56541698546289</v>
+      </c>
+      <c r="C14">
         <v>36.80183626625861</v>
-      </c>
-      <c r="C14">
-        <v>23.56541698546289</v>
       </c>
       <c r="D14">
         <v>2.717255717255717</v>
       </c>
       <c r="E14">
-        <v>22.94847328244275</v>
+        <v>14.69465648854962</v>
       </c>
       <c r="F14">
         <v>62.35687022900763</v>
       </c>
       <c r="G14">
-        <v>14.69465648854962</v>
+        <v>22.94847328244275</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.77706323687031</v>
+      </c>
+      <c r="C15">
         <v>28.76027152554484</v>
-      </c>
-      <c r="C15">
-        <v>25.77706323687031</v>
       </c>
       <c r="D15">
         <v>3.477018633540373</v>
       </c>
       <c r="E15">
-        <v>18.61056525257196</v>
+        <v>16.68015258351636</v>
       </c>
       <c r="F15">
         <v>64.70928216391168</v>
       </c>
       <c r="G15">
-        <v>16.68015258351636</v>
+        <v>18.61056525257196</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>22.00938232994527</v>
+      </c>
+      <c r="C16">
         <v>41.51681000781861</v>
-      </c>
-      <c r="C16">
-        <v>22.00938232994527</v>
       </c>
       <c r="D16">
         <v>2.408662900188324</v>
       </c>
       <c r="E16">
-        <v>25.38847716949558</v>
+        <v>13.45923978006216</v>
       </c>
       <c r="F16">
         <v>61.15228305044226</v>
       </c>
       <c r="G16">
-        <v>13.45923978006216</v>
+        <v>25.38847716949558</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>24.10901467505241</v>
+      </c>
+      <c r="C17">
         <v>36.37316561844864</v>
-      </c>
-      <c r="C17">
-        <v>24.10901467505241</v>
       </c>
       <c r="D17">
         <v>2.749279538904899</v>
       </c>
       <c r="E17">
-        <v>22.66492488569563</v>
+        <v>15.02286087524494</v>
       </c>
       <c r="F17">
         <v>62.31221423905944</v>
       </c>
       <c r="G17">
-        <v>15.02286087524494</v>
+        <v>22.66492488569563</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.58402838578867</v>
+      </c>
+      <c r="C18">
         <v>22.07271554306253</v>
-      </c>
-      <c r="C18">
-        <v>26.58402838578867</v>
       </c>
       <c r="D18">
         <v>4.530480167014614</v>
       </c>
       <c r="E18">
-        <v>14.84810911345319</v>
+        <v>17.88282703037818</v>
       </c>
       <c r="F18">
         <v>67.26906385616863</v>
       </c>
       <c r="G18">
-        <v>17.88282703037818</v>
+        <v>14.84810911345319</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>21.87445357579996</v>
+      </c>
+      <c r="C19">
         <v>40.19933554817276</v>
-      </c>
-      <c r="C19">
-        <v>21.87445357579996</v>
       </c>
       <c r="D19">
         <v>2.487603305785124</v>
       </c>
       <c r="E19">
-        <v>24.80310713129787</v>
+        <v>13.49660157514295</v>
       </c>
       <c r="F19">
-        <v>61.70029129355917</v>
+        <v>61.70029129355918</v>
       </c>
       <c r="G19">
-        <v>13.49660157514295</v>
+        <v>24.80310713129788</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>21.03383458646617</v>
+      </c>
+      <c r="C20">
         <v>38.43984962406015</v>
-      </c>
-      <c r="C20">
-        <v>21.03383458646617</v>
       </c>
       <c r="D20">
         <v>2.601466992665037</v>
       </c>
       <c r="E20">
+        <v>13.18953323903819</v>
+      </c>
+      <c r="F20">
+        <v>62.7062706270627</v>
+      </c>
+      <c r="G20">
         <v>24.10419613389911</v>
-      </c>
-      <c r="F20">
-        <v>62.70627062706271</v>
-      </c>
-      <c r="G20">
-        <v>13.18953323903819</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>24.64462134404208</v>
+      </c>
+      <c r="C21">
         <v>32.84143004371158</v>
-      </c>
-      <c r="C21">
-        <v>24.64462134404208</v>
       </c>
       <c r="D21">
         <v>3.044934397402949</v>
       </c>
       <c r="E21">
-        <v>20.85354845988943</v>
+        <v>15.64876452668397</v>
       </c>
       <c r="F21">
         <v>63.4976870134266</v>
       </c>
       <c r="G21">
-        <v>15.64876452668397</v>
+        <v>20.85354845988943</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.66574089201111</v>
+      </c>
+      <c r="C22">
         <v>39.45433752654795</v>
-      </c>
-      <c r="C22">
-        <v>25.66574089201111</v>
       </c>
       <c r="D22">
         <v>2.534575569358178</v>
       </c>
       <c r="E22">
-        <v>23.89433066191748</v>
+        <v>15.54368259622044</v>
       </c>
       <c r="F22">
         <v>60.56198674186207</v>
       </c>
       <c r="G22">
-        <v>15.54368259622044</v>
+        <v>23.89433066191748</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.40038192234246</v>
+      </c>
+      <c r="C23">
         <v>43.20496499045194</v>
-      </c>
-      <c r="C23">
-        <v>26.40038192234246</v>
       </c>
       <c r="D23">
         <v>2.314548802946593</v>
       </c>
       <c r="E23">
-        <v>25.47382248076562</v>
+        <v>15.5657721899043</v>
       </c>
       <c r="F23">
         <v>58.96040532933008</v>
       </c>
       <c r="G23">
-        <v>15.5657721899043</v>
+        <v>25.47382248076562</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>22.52729778437401</v>
+      </c>
+      <c r="C24">
         <v>38.2274992049189</v>
-      </c>
-      <c r="C24">
-        <v>22.52729778437401</v>
       </c>
       <c r="D24">
         <v>2.6159179145868</v>
       </c>
       <c r="E24">
-        <v>23.78000527565286</v>
+        <v>14.0134529147982</v>
       </c>
       <c r="F24">
         <v>62.20654180954893</v>
       </c>
       <c r="G24">
-        <v>14.0134529147982</v>
+        <v>23.78000527565286</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>24.31580018313155</v>
+      </c>
+      <c r="C25">
         <v>43.13765388137145</v>
-      </c>
-      <c r="C25">
-        <v>24.31580018313155</v>
       </c>
       <c r="D25">
         <v>2.31816037735849</v>
       </c>
       <c r="E25">
-        <v>25.76098183364724</v>
+        <v>14.52093079773984</v>
       </c>
       <c r="F25">
         <v>59.71808736861291</v>
       </c>
       <c r="G25">
-        <v>14.52093079773984</v>
+        <v>25.76098183364724</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>23.68896925858951</v>
+      </c>
+      <c r="C26">
         <v>49.26662648181635</v>
-      </c>
-      <c r="C26">
-        <v>23.68896925858951</v>
       </c>
       <c r="D26">
         <v>2.029771615008157</v>
       </c>
       <c r="E26">
-        <v>28.48513011152416</v>
+        <v>13.69656133828996</v>
       </c>
       <c r="F26">
         <v>57.81830855018588</v>
       </c>
       <c r="G26">
-        <v>13.69656133828996</v>
+        <v>28.48513011152416</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>22.39271457085828</v>
+      </c>
+      <c r="C27">
         <v>43.00149700598803</v>
-      </c>
-      <c r="C27">
-        <v>22.39271457085828</v>
       </c>
       <c r="D27">
         <v>2.32550043516101</v>
       </c>
       <c r="E27">
-        <v>25.99939659073767</v>
+        <v>13.53899532357821</v>
       </c>
       <c r="F27">
         <v>60.46160808568411</v>
       </c>
       <c r="G27">
-        <v>13.53899532357821</v>
+        <v>25.99939659073767</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>23.35234474017744</v>
+      </c>
+      <c r="C28">
         <v>33.61850443599493</v>
-      </c>
-      <c r="C28">
-        <v>23.35234474017744</v>
       </c>
       <c r="D28">
         <v>2.974552309142318</v>
       </c>
       <c r="E28">
-        <v>21.4170367379895</v>
+        <v>14.87686717803795</v>
       </c>
       <c r="F28">
         <v>63.70609608397255</v>
       </c>
       <c r="G28">
-        <v>14.87686717803795</v>
+        <v>21.4170367379895</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.21345707656612</v>
+      </c>
+      <c r="C29">
         <v>33.82830626450117</v>
-      </c>
-      <c r="C29">
-        <v>28.21345707656612</v>
       </c>
       <c r="D29">
         <v>2.956104252400549</v>
       </c>
       <c r="E29">
-        <v>20.87628865979381</v>
+        <v>17.41122565864834</v>
       </c>
       <c r="F29">
-        <v>61.71248568155784</v>
+        <v>61.71248568155785</v>
       </c>
       <c r="G29">
-        <v>17.41122565864833</v>
+        <v>20.87628865979382</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>22.27672955974843</v>
+      </c>
+      <c r="C30">
         <v>29.71069182389937</v>
-      </c>
-      <c r="C30">
-        <v>22.27672955974843</v>
       </c>
       <c r="D30">
         <v>3.365791701947502</v>
       </c>
       <c r="E30">
-        <v>19.54812546553008</v>
+        <v>14.65695605396011</v>
       </c>
       <c r="F30">
         <v>65.79491848050981</v>
       </c>
       <c r="G30">
-        <v>14.65695605396011</v>
+        <v>19.54812546553008</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.4375</v>
+      </c>
+      <c r="C31">
         <v>39.12760416666667</v>
-      </c>
-      <c r="C31">
-        <v>23.4375</v>
       </c>
       <c r="D31">
         <v>2.555740432612313</v>
       </c>
       <c r="E31">
-        <v>24.06888265919103</v>
+        <v>14.41730076091309</v>
       </c>
       <c r="F31">
         <v>61.51381657989587</v>
       </c>
       <c r="G31">
-        <v>14.41730076091309</v>
+        <v>24.06888265919103</v>
       </c>
     </row>
   </sheetData>
